--- a/Week_9/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_9/Capstone Timesheet_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="87">
   <si>
     <t>Week_1</t>
   </si>
@@ -262,6 +262,15 @@
     <t>Connected patient dashboard with database to display upcoming and recent appointments dynamically.</t>
   </si>
   <si>
+    <t>Create New page for patient (record page)  + connect with databse</t>
+  </si>
+  <si>
+    <t>Create New page for patient (Edit appointment) + connect with databse</t>
+  </si>
+  <si>
+    <t>Fully Dynamic Patient Pofile ready  + Testing</t>
+  </si>
+  <si>
     <t>Total Hours</t>
   </si>
 </sst>
@@ -427,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -667,9 +676,6 @@
     </xf>
     <xf borderId="1" fillId="12" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="12" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="12" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -4612,9 +4618,15 @@
     </row>
     <row r="110">
       <c r="A110" s="79"/>
-      <c r="B110" s="83"/>
-      <c r="C110" s="84"/>
-      <c r="D110" s="82"/>
+      <c r="B110" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="C110" s="81">
+        <v>46094.0</v>
+      </c>
+      <c r="D110" s="82">
+        <v>1.75</v>
+      </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
@@ -4641,9 +4653,15 @@
     </row>
     <row r="111">
       <c r="A111" s="79"/>
-      <c r="B111" s="83"/>
-      <c r="C111" s="81"/>
-      <c r="D111" s="82"/>
+      <c r="B111" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="C111" s="81">
+        <v>46094.0</v>
+      </c>
+      <c r="D111" s="82">
+        <v>2.75</v>
+      </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
@@ -4670,9 +4688,15 @@
     </row>
     <row r="112">
       <c r="A112" s="79"/>
-      <c r="B112" s="83"/>
-      <c r="C112" s="81"/>
-      <c r="D112" s="82"/>
+      <c r="B112" s="83" t="s">
+        <v>85</v>
+      </c>
+      <c r="C112" s="81">
+        <v>46094.0</v>
+      </c>
+      <c r="D112" s="82">
+        <v>3.5</v>
+      </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
@@ -4727,10 +4751,10 @@
       <c r="AA113" s="3"/>
     </row>
     <row r="114">
-      <c r="A114" s="85"/>
+      <c r="A114" s="84"/>
       <c r="B114" s="80"/>
       <c r="C114" s="81"/>
-      <c r="D114" s="86"/>
+      <c r="D114" s="85"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
@@ -4756,10 +4780,10 @@
       <c r="AA114" s="3"/>
     </row>
     <row r="115">
-      <c r="A115" s="85"/>
+      <c r="A115" s="84"/>
       <c r="B115" s="80"/>
       <c r="C115" s="81"/>
-      <c r="D115" s="86"/>
+      <c r="D115" s="85"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
@@ -4785,10 +4809,10 @@
       <c r="AA115" s="3"/>
     </row>
     <row r="116">
-      <c r="A116" s="85"/>
+      <c r="A116" s="84"/>
       <c r="B116" s="80"/>
       <c r="C116" s="81"/>
-      <c r="D116" s="86"/>
+      <c r="D116" s="85"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
@@ -4814,10 +4838,10 @@
       <c r="AA116" s="3"/>
     </row>
     <row r="117">
-      <c r="A117" s="85"/>
-      <c r="B117" s="87"/>
+      <c r="A117" s="84"/>
+      <c r="B117" s="86"/>
       <c r="C117" s="81"/>
-      <c r="D117" s="86"/>
+      <c r="D117" s="85"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
@@ -4843,10 +4867,10 @@
       <c r="AA117" s="3"/>
     </row>
     <row r="118">
-      <c r="A118" s="85"/>
-      <c r="B118" s="87"/>
+      <c r="A118" s="84"/>
+      <c r="B118" s="86"/>
       <c r="C118" s="81"/>
-      <c r="D118" s="86"/>
+      <c r="D118" s="85"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
@@ -4872,10 +4896,10 @@
       <c r="AA118" s="3"/>
     </row>
     <row r="119">
-      <c r="A119" s="88"/>
+      <c r="A119" s="87"/>
       <c r="B119" s="83"/>
       <c r="C119" s="81"/>
-      <c r="D119" s="89"/>
+      <c r="D119" s="88"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
@@ -4901,10 +4925,10 @@
       <c r="AA119" s="3"/>
     </row>
     <row r="120">
-      <c r="A120" s="88"/>
+      <c r="A120" s="87"/>
       <c r="B120" s="83"/>
       <c r="C120" s="81"/>
-      <c r="D120" s="89"/>
+      <c r="D120" s="88"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -4930,10 +4954,10 @@
       <c r="AA120" s="3"/>
     </row>
     <row r="121">
-      <c r="A121" s="88"/>
+      <c r="A121" s="87"/>
       <c r="B121" s="83"/>
       <c r="C121" s="81"/>
-      <c r="D121" s="89"/>
+      <c r="D121" s="88"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
@@ -4959,10 +4983,10 @@
       <c r="AA121" s="3"/>
     </row>
     <row r="122">
-      <c r="A122" s="88"/>
-      <c r="B122" s="90"/>
+      <c r="A122" s="87"/>
+      <c r="B122" s="89"/>
       <c r="C122" s="81"/>
-      <c r="D122" s="89"/>
+      <c r="D122" s="88"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
@@ -4988,14 +5012,14 @@
       <c r="AA122" s="3"/>
     </row>
     <row r="123">
-      <c r="A123" s="88"/>
-      <c r="B123" s="90" t="s">
+      <c r="A123" s="87"/>
+      <c r="B123" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="C123" s="91"/>
+      <c r="C123" s="90"/>
       <c r="D123" s="79">
         <f>sum(D109:D122)</f>
-        <v>2.75</v>
+        <v>10.75</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -5863,14 +5887,14 @@
       <c r="AA152" s="3"/>
     </row>
     <row r="153">
-      <c r="A153" s="92" t="s">
-        <v>83</v>
+      <c r="A153" s="91" t="s">
+        <v>86</v>
       </c>
-      <c r="B153" s="93"/>
-      <c r="C153" s="93"/>
-      <c r="D153" s="94">
+      <c r="B153" s="92"/>
+      <c r="C153" s="92"/>
+      <c r="D153" s="93">
         <f>sum(D14,D34,D44,D54,D63,D73,D87,D105,D123)</f>
-        <v>170.6</v>
+        <v>178.6</v>
       </c>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
